--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -92,10 +92,10 @@
     <t>double</t>
   </si>
   <si>
-    <t>盘古斧</t>
-  </si>
-  <si>
-    <t>攻击会触发幸运一击，额外增加幸运*{0}%的伤害（乘法）</t>
+    <t>青龙之力</t>
+  </si>
+  <si>
+    <t>攻击会触发幸运一击，额外增加幸运*{0}%（下一级+{1}）的伤害（乘法）</t>
   </si>
   <si>
     <t>轩辕剑</t>
@@ -286,12 +286,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1163,7 +1163,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="1">
-        <v>2003</v>
+        <v>117</v>
       </c>
       <c r="F6" s="1">
         <v>0.01</v>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1166,7 +1166,7 @@
         <v>117</v>
       </c>
       <c r="F6" s="1">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -98,10 +98,13 @@
     <t>攻击会触发幸运一击，额外增加幸运*{0}%（下一级+{1}）的伤害（乘法）</t>
   </si>
   <si>
-    <t>轩辕剑</t>
-  </si>
-  <si>
-    <t>防御倍率</t>
+    <t>白虎之命</t>
+  </si>
+  <si>
+    <t>每点减伤属性额外提高生命*{0}%（下一级+{1}）（乘法）</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>神农鼎</t>
@@ -1076,13 +1079,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I8"/>
+  <dimension ref="A3:I8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
-    <col min="5" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6283185840708" style="1" customWidth="1"/>
+    <col min="5" max="8" width="12.2477876106195" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.8761061946903" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1186,24 +1189,33 @@
         <v>12</v>
       </c>
       <c r="E7" s="1">
-        <v>2002</v>
+        <v>118</v>
       </c>
       <c r="F7" s="1">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="1">
-        <v>30</v>
+        <v>3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:9">
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1">
         <v>2001</v>
@@ -1215,7 +1227,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -289,12 +289,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1195,7 +1195,7 @@
         <v>0.5</v>
       </c>
       <c r="G7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -104,13 +104,10 @@
     <t>每点减伤属性额外提高生命*{0}%（下一级+{1}）（乘法）</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>神农鼎</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 攻击倍率</t>
+    <t>朱雀之神</t>
+  </si>
+  <si>
+    <t>额外增加命中*{0}%（下一级+{1}）的伤害（乘法）</t>
   </si>
 </sst>
 </file>
@@ -289,12 +286,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1079,7 +1076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I8"/>
+  <dimension ref="C3:I8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1204,30 +1201,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="8" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1">
+        <v>119</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2001</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1">
-        <v>5</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t>Id</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>额外增加命中*{0}%（下一级+{1}）的伤害（乘法）</t>
+  </si>
+  <si>
+    <t>玄武之破</t>
+  </si>
+  <si>
+    <t>降低敌人闪避*{0}倍（下一级+{1}）的韧性（乘法）</t>
   </si>
 </sst>
 </file>
@@ -1076,13 +1082,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelRow="7"/>
+  <dimension ref="C3:I9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="12.6283185840708" style="1" customWidth="1"/>
-    <col min="5" max="8" width="12.2477876106195" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.8761061946903" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="5" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1149,7 +1155,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>8</v>
@@ -1222,6 +1228,29 @@
       </c>
       <c r="I8" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:9">
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>120</v>
+      </c>
+      <c r="F9" s="1">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -107,13 +107,13 @@
     <t>朱雀之神</t>
   </si>
   <si>
-    <t>额外增加命中*{0}%（下一级+{1}）的伤害（乘法）</t>
+    <t>额外增加(自身命中*{0})%（下一级+{1}）的伤害（乘法）</t>
   </si>
   <si>
     <t>玄武之破</t>
   </si>
   <si>
-    <t>降低敌人闪避*{0}倍（下一级+{1}）的韧性（乘法）</t>
+    <t>降低敌人(自身闪避*{0})倍（下一级+{1}）的韧性（乘法）</t>
   </si>
 </sst>
 </file>
@@ -1241,13 +1241,13 @@
         <v>120</v>
       </c>
       <c r="F9" s="1">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H9" s="1">
         <v>2</v>
-      </c>
-      <c r="H9" s="1">
-        <v>2.5</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>17</v>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -1175,7 +1175,7 @@
         <v>0.1</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
@@ -1198,7 +1198,7 @@
         <v>0.5</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>
@@ -1221,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="H8" s="1">
         <v>2</v>
@@ -1244,7 +1244,7 @@
         <v>0.1</v>
       </c>
       <c r="G9" s="1">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -1241,10 +1241,10 @@
         <v>120</v>
       </c>
       <c r="F9" s="1">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>Id</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>降低敌人(自身闪避*{0})倍（下一级+{1}）的韧性（乘法）</t>
+  </si>
+  <si>
+    <t>麒麟之速</t>
+  </si>
+  <si>
+    <t>额外增加(自身攻速*{0})%（下一级+{1}）的伤害（乘法）</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I9"/>
+  <dimension ref="C3:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1253,6 +1259,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" customHeight="1" spans="3:9">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="1">
+        <v>121</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -68,6 +68,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Cyle</t>
+  </si>
+  <si>
     <t>AttrId</t>
   </si>
   <si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>额外增加(自身攻速*{0})%（下一级+{1}）的伤害（乘法）</t>
+  </si>
+  <si>
+    <t>极龙之力</t>
   </si>
 </sst>
 </file>
@@ -1088,17 +1094,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I10"/>
+  <dimension ref="C3:J11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
-    <col min="5" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="4" max="5" width="12.625" style="1" customWidth="1"/>
+    <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="40.875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1120,8 +1126,11 @@
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1143,148 +1152,195 @@
       <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="6" customHeight="1" spans="3:9">
+    <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
         <v>117</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>0.1</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>2.24</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>11</v>
+      <c r="J6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:9">
+    <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
         <v>118</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>0.5</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>2.24</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>13</v>
+      <c r="J7" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:9">
+    <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
         <v>119</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>10</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>2.24</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>15</v>
+      <c r="J8" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:9">
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
         <v>120</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>10</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>3.5</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>2</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>17</v>
+      <c r="J9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:9">
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
         <v>121</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>10</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>3</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>19</v>
+      <c r="J10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:10">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>117</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>Id</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>极龙之力</t>
+  </si>
+  <si>
+    <t>青龙之力的伤害提高{0}%（下一级+{1}）的伤害</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>117</v>
+        <v>3117</v>
       </c>
       <c r="G6" s="1">
         <v>0.1</v>
@@ -1219,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>118</v>
+        <v>3118</v>
       </c>
       <c r="G7" s="1">
         <v>0.5</v>
@@ -1245,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>119</v>
+        <v>3119</v>
       </c>
       <c r="G8" s="1">
         <v>10</v>
@@ -1271,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>120</v>
+        <v>3120</v>
       </c>
       <c r="G9" s="1">
         <v>10</v>
@@ -1297,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>121</v>
+        <v>3121</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -1323,24 +1326,24 @@
         <v>2</v>
       </c>
       <c r="F11" s="1">
-        <v>117</v>
+        <v>3117</v>
       </c>
       <c r="G11" s="1">
-        <v>0.1</v>
+        <v>200</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -307,12 +307,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1329,7 +1329,7 @@
         <v>3117</v>
       </c>
       <c r="G11" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H11" s="1">
         <v>3</v>

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>青龙之力的伤害提高{0}%（下一级+{1}）的伤害</t>
+  </si>
+  <si>
+    <t>极虎之力</t>
+  </si>
+  <si>
+    <t>白虎之命的血量提高{0}%（下一级+{1}）</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J11"/>
+  <dimension ref="C3:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1341,6 +1347,32 @@
         <v>22</v>
       </c>
     </row>
+    <row r="12" customHeight="1" spans="3:10">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3118</v>
+      </c>
+      <c r="G12" s="1">
+        <v>300</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">

--- a/Excel/RelicGroupConfig.xlsx
+++ b/Excel/RelicGroupConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -60,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -131,10 +136,16 @@
     <t>青龙之力的伤害提高{0}%（下一级+{1}）的伤害</t>
   </si>
   <si>
-    <t>极虎之力</t>
+    <t>极虎之命</t>
   </si>
   <si>
     <t>白虎之命的血量提高{0}%（下一级+{1}）</t>
+  </si>
+  <si>
+    <t>极雀之神</t>
+  </si>
+  <si>
+    <t>朱雀之神的伤害提高{0}%（下一级+{1}）</t>
   </si>
 </sst>
 </file>
@@ -313,12 +324,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1103,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J12"/>
+  <dimension ref="C3:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1373,6 +1384,32 @@
         <v>24</v>
       </c>
     </row>
+    <row r="13" customHeight="1" spans="3:10">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1">
+        <v>3119</v>
+      </c>
+      <c r="G13" s="1">
+        <v>300</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
